--- a/EXCEL/Exercise Files/Chapter05/Chapter_5_Challenge.xlsx
+++ b/EXCEL/Exercise Files/Chapter05/Chapter_5_Challenge.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter05\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85454552-0629-4506-B885-B58E4EE0E59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5981B67-B4E2-4189-A026-0B24D1099E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{CACA7FB2-60B5-4A3B-9AD0-6B713E1BE737}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" xr2:uid="{CACA7FB2-60B5-4A3B-9AD0-6B713E1BE737}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -61,7 +59,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -114,14 +112,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -439,17 +437,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B6D481-E7BA-4852-82DC-2EC3A36916DB}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.07421875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.84375" customWidth="1"/>
-    <col min="5" max="5" width="29.921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="11.921875" customWidth="1"/>
-    <col min="9" max="9" width="10.765625" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.88671875" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="11.88671875" customWidth="1"/>
+    <col min="9" max="9" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -460,7 +458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26</v>
       </c>
@@ -473,8 +471,12 @@
       <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="F2">
+        <f>_xlfn.COVARIANCE.S(A2:A12,B2:B12)</f>
+        <v>4023.1636363636362</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>21</v>
       </c>
@@ -485,7 +487,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>21</v>
       </c>
@@ -498,8 +500,12 @@
       <c r="E4" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="F4">
+        <f>CORREL(A2:A12,B2:B12)</f>
+        <v>0.84282187851724777</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>39</v>
       </c>
@@ -510,7 +516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>43</v>
       </c>
@@ -524,7 +530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>13</v>
       </c>
@@ -544,7 +550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>24</v>
       </c>
@@ -557,8 +563,20 @@
       <c r="F8" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="G8">
+        <f>CORREL($A$2:$A$12,A2:A12)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="H8">
+        <f t="shared" ref="H8:I8" si="0">CORREL($A$2:$A$12,B2:B12)</f>
+        <v>0.84282187851724777</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>-3.9432931863085739E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>10</v>
       </c>
@@ -571,8 +589,20 @@
       <c r="F9" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.9" x14ac:dyDescent="0.45">
+      <c r="G9">
+        <f>CORREL($B$2:$B$12,A2:A12)</f>
+        <v>0.84282187851724777</v>
+      </c>
+      <c r="H9">
+        <f t="shared" ref="H9:I9" si="1">CORREL($B$2:$B$12,B2:B12)</f>
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>0.12598828403800352</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>30</v>
       </c>
@@ -585,8 +615,20 @@
       <c r="F10" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="G10">
+        <f>CORREL($C$2:$C$12,A2:A12)</f>
+        <v>-3.9432931863085739E-2</v>
+      </c>
+      <c r="H10">
+        <f t="shared" ref="H10:I10" si="2">CORREL($C$2:$C$12,B2:B12)</f>
+        <v>0.12598828403800352</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>31</v>
       </c>
@@ -597,7 +639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25</v>
       </c>
